--- a/duoki_editor/resources/data/blank/动物园-一般疑问句_问句跟读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/动物园-一般疑问句_问句跟读-1-blank.xlsx
@@ -130,7 +130,7 @@
     <t>`我来帮你吧！[{word_en}]`</t>
   </si>
   <si>
-    <t>太棒了！动物朋友们的乐队表演真精彩呀！{user_name}，你来提问吧，考考我是不是认识这些朋友！</t>
+    <t>太棒了！动物朋友们的乐队表演真精彩呀！{user_name}，问这是不是某种动物，该如何提问呢？我们一起来学习吧！</t>
   </si>
   <si>
     <t>{user_name}，你接着问吧。</t>
